--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5763</v>
+        <v>22.2583</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6775</v>
+        <v>14.0319</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8988</v>
+        <v>8.2263</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5518</v>
+        <v>7.4787</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7371</v>
+        <v>5.2332</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8146</v>
+        <v>2.2454</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7842</v>
+        <v>6.6796</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8244</v>
+        <v>4.7343</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9599000000000001</v>
+        <v>1.9453</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7674999999999998</v>
+        <v>0.7992</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.08719999999999994</v>
+        <v>0.4991</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8548</v>
+        <v>0.3002</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2004</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>4.0894</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8241</v>
+        <v>6.2012</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6938</v>
+        <v>2.3046</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1304</v>
+        <v>3.8965</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.436299999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1998</v>
+        <v>6.9953</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1998</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.774999999999999</v>
+        <v>15.258</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5568</v>
+        <v>13.936</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7818</v>
+        <v>1.322</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4267</v>
+        <v>7.4673</v>
       </c>
       <c r="H3" t="n">
-        <v>5.043699999999999</v>
+        <v>11.2673</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.6171</v>
+        <v>-3.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5298</v>
+        <v>12.6681</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3239</v>
+        <v>10.9485</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.794</v>
+        <v>1.7194</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1032</v>
+        <v>-5.2006</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2802</v>
+        <v>0.3189000000000002</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8229</v>
+        <v>-5.5194</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8002</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2009</v>
+        <v>-7.9842</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4007</v>
+        <v>5.452500000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9494</v>
+        <v>3.2797</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0495</v>
+        <v>1.139</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1001</v>
+        <v>2.1407</v>
       </c>
       <c r="V3" t="n">
-        <v>4.1992</v>
+        <v>7.0425</v>
       </c>
       <c r="W3" t="n">
-        <v>6.1784</v>
+        <v>8.113199999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.9791</v>
+        <v>-1.0707</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4595</v>
+        <v>7.938899999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>9.027100000000001</v>
+        <v>2.2306</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.5676</v>
+        <v>5.7083</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0954</v>
+        <v>4.7941</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2019</v>
+        <v>3.9985</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8935</v>
+        <v>0.7957000000000005</v>
       </c>
       <c r="J4" t="n">
-        <v>6.5479</v>
+        <v>4.3593</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8246</v>
+        <v>3.0535</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7232</v>
+        <v>1.3058</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4525</v>
+        <v>0.4348000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6227</v>
+        <v>0.9450000000000002</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8298</v>
+        <v>-0.5103000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6001</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2004</v>
+        <v>-7.5948</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8005</v>
+        <v>5.0632</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08379999999999999</v>
+        <v>3.2858</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08019999999999999</v>
+        <v>1.9059</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003599999999999999</v>
+        <v>1.3798</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6801999999999999</v>
+        <v>2.3906</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5993</v>
+        <v>3.5601</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.9192</v>
+        <v>-1.1694</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3509</v>
+        <v>6.0375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3036000000000001</v>
+        <v>8.989799999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0474</v>
+        <v>-2.9523</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2508</v>
+        <v>4.7471</v>
       </c>
       <c r="H5" t="n">
-        <v>2.753</v>
+        <v>4.6846</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5022</v>
+        <v>0.0625</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9108000000000001</v>
+        <v>9.2334</v>
       </c>
       <c r="K5" t="n">
-        <v>2.183</v>
+        <v>5.1395</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2722</v>
+        <v>4.0938</v>
       </c>
       <c r="M5" t="n">
-        <v>0.34</v>
+        <v>-4.4862</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5701000000000001</v>
+        <v>-0.4549000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.23</v>
+        <v>-4.0312</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2000000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.4004</v>
+        <v>-5.0632</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6004</v>
+        <v>4.8685</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3804999999999998</v>
+        <v>-1.3352</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2736</v>
+        <v>-1.5652</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1069</v>
+        <v>0.2299</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5196</v>
+        <v>2.820399999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5196</v>
+        <v>6.3848</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.5643</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RUIZ CANAMERO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,67 +874,67 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.131</v>
+        <v>5.7948</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2655</v>
+        <v>5.7948</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8653999999999999</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3378</v>
+        <v>5.7948</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9797</v>
+        <v>1.5395</v>
       </c>
       <c r="I6" t="n">
-        <v>0.358</v>
+        <v>4.2553</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9815</v>
+        <v>5.7948</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9016</v>
+        <v>1.5395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08</v>
+        <v>4.2553</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3562</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07820000000000001</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2781</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4001</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4001</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4066</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5157</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1091</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1998</v>
+        <v>4.542100000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1998</v>
+        <v>3.423100000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.119</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1998</v>
+        <v>4.795100000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.9963</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1998</v>
+        <v>2.7986</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1998</v>
+        <v>9.2759</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.692</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1998</v>
+        <v>6.584</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-4.4808</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.6957</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-3.7851</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.3894000000000002</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-6.0369</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.6475</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.4695999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-1.9271</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.4574</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6061000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.111</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5049</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. COSTA I VAZQUEZ</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4895</v>
+        <v>4.0179</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06699999999999973</v>
+        <v>0.9297000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5565</v>
+        <v>3.088</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000300000000000189</v>
+        <v>3.422800000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4521999999999999</v>
+        <v>3.9467</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4525000000000001</v>
+        <v>-0.5239000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2531</v>
+        <v>4.714399999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3581</v>
+        <v>4.4623</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6112</v>
+        <v>0.2522</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2528</v>
+        <v>-1.2915</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.09409999999999985</v>
+        <v>-0.5156000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1587</v>
+        <v>-0.7759999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2003</v>
+        <v>2.142</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4004</v>
+        <v>-1.5579</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6007</v>
+        <v>3.7</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4514</v>
+        <v>-1.0569</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0803</v>
+        <v>-2.0718</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5317</v>
+        <v>1.015</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2598</v>
+        <v>-0.4901</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.1547999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2598</v>
+        <v>-0.3354</v>
       </c>
     </row>
     <row r="9">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05210000000000004</v>
+        <v>2.3213</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3525</v>
+        <v>1.1409</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4046</v>
+        <v>1.1806</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0959</v>
+        <v>1.6889</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8977</v>
+        <v>2.6633</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8018000000000001</v>
+        <v>-0.9742999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0615</v>
+        <v>1.7531</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6195</v>
+        <v>2.263</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5102</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0343</v>
+        <v>-0.06410000000000005</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2781</v>
+        <v>0.4002</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2438</v>
+        <v>-0.4643999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0003</v>
+        <v>1.3631</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2001</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2004</v>
+        <v>2.5315</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9484999999999999</v>
+        <v>0.3185000000000002</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5089999999999999</v>
+        <v>0.04899999999999993</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4395</v>
+        <v>0.2696</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1998</v>
+        <v>-1.0491</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5073</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1998</v>
+        <v>-1.5565</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4064</v>
+        <v>1.2147</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9565</v>
+        <v>0.8772</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5502</v>
+        <v>0.3375999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0841</v>
+        <v>2.2114</v>
       </c>
       <c r="H10" t="n">
-        <v>0.265</v>
+        <v>1.8341</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3491</v>
+        <v>0.3772</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2542</v>
+        <v>1.1742</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7797999999999999</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.034</v>
+        <v>0.2837</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1701</v>
+        <v>1.0371</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5147999999999999</v>
+        <v>0.9435</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6849000000000001</v>
+        <v>0.09339999999999998</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8003</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.7527</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8003</v>
+        <v>1.9473</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1225</v>
+        <v>0.3091</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7022999999999999</v>
+        <v>0.2344</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4202</v>
+        <v>0.07449999999999998</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7687</v>
+        <v>0.2532000000000005</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6931</v>
+        <v>-1.7564</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0755</v>
+        <v>2.0097</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.008600000000000052</v>
+        <v>-5.3265</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4016999999999999</v>
+        <v>-1.6254</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3931</v>
+        <v>-3.701</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0073</v>
+        <v>-2.826</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0415</v>
+        <v>-3.8403</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0343</v>
+        <v>1.0145</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0158</v>
+        <v>-2.5006</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4432</v>
+        <v>2.215</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4274</v>
+        <v>-4.7154</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2001</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2001</v>
+        <v>-7.9842</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4001</v>
+        <v>6.426299999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.62</v>
+        <v>8.027699999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1602</v>
+        <v>4.7799</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4598</v>
+        <v>3.2476</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3401</v>
+        <v>-0.8898999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3401</v>
+        <v>4.2737</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-5.1638</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.276</v>
+        <v>-0.6024</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1827</v>
+        <v>-4.9772</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.09329999999999999</v>
+        <v>4.3748</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9579</v>
+        <v>-2.2158</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6428</v>
+        <v>1.723</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3149999999999999</v>
+        <v>-3.9389</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1393</v>
+        <v>-2.1244</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.5048</v>
+        <v>0.3541000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3655</v>
+        <v>-2.4786</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8184999999999999</v>
+        <v>-0.09150000000000003</v>
       </c>
       <c r="N12" t="n">
-        <v>0.862</v>
+        <v>1.3688</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6805</v>
+        <v>-1.4601</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6002000000000001</v>
+        <v>2.921</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.2009</v>
+        <v>-2.7264</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6007</v>
+        <v>5.6474</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4817</v>
+        <v>-2.5286</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2421</v>
+        <v>-1.6271</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7238</v>
+        <v>-0.9016000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1997</v>
+        <v>1.221</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3995</v>
+        <v>1.5005</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5993</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2777</v>
+        <v>-6.111499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1691</v>
+        <v>-8.860099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.4468</v>
+        <v>2.7487</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8632</v>
+        <v>-6.450900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6975</v>
+        <v>-0.5721999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.5607</v>
+        <v>-5.8787</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2058</v>
+        <v>-6.3775</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2284</v>
+        <v>0.2591000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0226</v>
+        <v>-6.636699999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.069</v>
+        <v>-0.07340000000000013</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4690000000000001</v>
+        <v>-0.8314</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5381</v>
+        <v>0.7579999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4004</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.6004</v>
+        <v>-1.3632</v>
       </c>
       <c r="R13" t="n">
-        <v>3.0008</v>
+        <v>1.9473</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9552</v>
+        <v>-0.6274000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0356</v>
+        <v>-1.1194</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9196</v>
+        <v>0.492</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8597000000000001</v>
+        <v>0.3826</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5993</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.459</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.373500000000001</v>
+        <v>-8.0909</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.3507</v>
+        <v>-6.947</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.02280000000000004</v>
+        <v>-1.1439</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6571</v>
+        <v>-6.2154</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.336</v>
+        <v>2.3779</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3210999999999999</v>
+        <v>-8.5932</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6318999999999999</v>
+        <v>-3.0806</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9271</v>
+        <v>1.4552</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2950999999999999</v>
+        <v>-4.5358</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0252</v>
+        <v>-3.1348</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4089</v>
+        <v>0.9227000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6163</v>
+        <v>-4.0575</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.2003</v>
+        <v>0.7789</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.2009</v>
+        <v>-5.4526</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0006</v>
+        <v>6.2314</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3163</v>
+        <v>-2.0956</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1779</v>
+        <v>-2.6875</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1385</v>
+        <v>0.5919</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1998</v>
+        <v>-0.5589999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3401</v>
+        <v>4.2737</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8597</v>
+        <v>-4.8326</v>
       </c>
     </row>
     <row r="15">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>13.8276</v>
+        <v>54.8319</v>
       </c>
       <c r="E15" t="n">
-        <v>16.3019</v>
+        <v>28.8133</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4741</v>
+        <v>26.0188</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3876</v>
+        <v>22.19159999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>15.7429</v>
+        <v>39.06679999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.355499999999999</v>
+        <v>-16.8753</v>
       </c>
       <c r="J15" t="n">
-        <v>18.4563</v>
+        <v>41.2443</v>
       </c>
       <c r="K15" t="n">
-        <v>16.9367</v>
+        <v>33.9513</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5196</v>
+        <v>7.292699999999996</v>
       </c>
       <c r="M15" t="n">
-        <v>-8.068900000000003</v>
+        <v>-19.0524</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1937</v>
+        <v>5.1156</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.8749</v>
+        <v>-24.1678</v>
       </c>
       <c r="P15" t="n">
-        <v>4.001199999999999</v>
+        <v>2.9208</v>
       </c>
       <c r="Q15" t="n">
-        <v>-17.0049</v>
+        <v>-50.6319</v>
       </c>
       <c r="R15" t="n">
-        <v>21.0059</v>
+        <v>53.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.101000000000001</v>
+        <v>13.3087</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.1654</v>
+        <v>-0.5853000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0644</v>
+        <v>13.8933</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5399</v>
+        <v>16.4109</v>
       </c>
       <c r="W15" t="n">
-        <v>18.0155</v>
+        <v>38.7859</v>
       </c>
       <c r="X15" t="n">
-        <v>-16.4757</v>
+        <v>-22.3751</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>22.2583</v>
+        <v>19.6726</v>
       </c>
       <c r="E2" t="n">
-        <v>14.0319</v>
+        <v>12.822</v>
       </c>
       <c r="F2" t="n">
-        <v>8.2263</v>
+        <v>6.8505</v>
       </c>
       <c r="G2" t="n">
         <v>7.4787</v>
@@ -610,13 +610,13 @@
         <v>4.0894</v>
       </c>
       <c r="S2" t="n">
-        <v>6.2012</v>
+        <v>3.6153</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3046</v>
+        <v>1.0947</v>
       </c>
       <c r="U2" t="n">
-        <v>3.8965</v>
+        <v>2.5207</v>
       </c>
       <c r="V2" t="n">
         <v>6.436299999999999</v>
@@ -643,13 +643,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>15.258</v>
+        <v>14.85</v>
       </c>
       <c r="E3" t="n">
-        <v>13.936</v>
+        <v>13.3859</v>
       </c>
       <c r="F3" t="n">
-        <v>1.322</v>
+        <v>1.4641</v>
       </c>
       <c r="G3" t="n">
         <v>7.4673</v>
@@ -688,13 +688,13 @@
         <v>5.452500000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2797</v>
+        <v>2.8716</v>
       </c>
       <c r="T3" t="n">
-        <v>1.139</v>
+        <v>0.5889</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1407</v>
+        <v>2.2827</v>
       </c>
       <c r="V3" t="n">
         <v>7.0425</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>7.938899999999999</v>
+        <v>8.2066</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2306</v>
+        <v>10.1481</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7083</v>
+        <v>-1.9414</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7941</v>
+        <v>4.7471</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9985</v>
+        <v>4.6846</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7957000000000005</v>
+        <v>0.0625</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3593</v>
+        <v>9.2334</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0535</v>
+        <v>5.1395</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3058</v>
+        <v>4.0938</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4348000000000001</v>
+        <v>-4.4862</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9450000000000002</v>
+        <v>-0.4549000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5103000000000001</v>
+        <v>-4.0312</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.5316</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-7.5948</v>
+        <v>-5.0632</v>
       </c>
       <c r="R4" t="n">
-        <v>5.0632</v>
+        <v>4.8685</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2858</v>
+        <v>0.8338000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9059</v>
+        <v>-0.407</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3798</v>
+        <v>1.2408</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3906</v>
+        <v>2.820399999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5601</v>
+        <v>6.3848</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1694</v>
+        <v>-3.5643</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0375</v>
+        <v>7.5867</v>
       </c>
       <c r="E5" t="n">
-        <v>8.989799999999999</v>
+        <v>5.6021</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.9523</v>
+        <v>1.9846</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7471</v>
+        <v>4.795100000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6846</v>
+        <v>1.9963</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0625</v>
+        <v>2.7986</v>
       </c>
       <c r="J5" t="n">
-        <v>9.2334</v>
+        <v>9.2759</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1395</v>
+        <v>2.692</v>
       </c>
       <c r="L5" t="n">
-        <v>4.0938</v>
+        <v>6.584</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.4862</v>
+        <v>-4.4808</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4549000000000001</v>
+        <v>-0.6957</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.0312</v>
+        <v>-3.7851</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1947</v>
+        <v>-0.3894000000000002</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.0632</v>
+        <v>-6.0369</v>
       </c>
       <c r="R5" t="n">
-        <v>4.8685</v>
+        <v>5.6475</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3352</v>
+        <v>2.5749</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.5652</v>
+        <v>0.2519999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2299</v>
+        <v>2.3229</v>
       </c>
       <c r="V5" t="n">
-        <v>2.820399999999999</v>
+        <v>0.6061000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>6.3848</v>
+        <v>2.111</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.5643</v>
+        <v>-1.5049</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5.7948</v>
+        <v>6.378</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7948</v>
+        <v>0.7593999999999996</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5.6187</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7948</v>
+        <v>4.7941</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5395</v>
+        <v>3.9985</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2553</v>
+        <v>0.7957000000000005</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7948</v>
+        <v>4.3593</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5395</v>
+        <v>3.0535</v>
       </c>
       <c r="L6" t="n">
-        <v>4.2553</v>
+        <v>1.3058</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.4348000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.9450000000000002</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.5103000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-7.5948</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>5.0632</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.725</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4347</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.2902</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.3906</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.5601</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1694</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4.542100000000001</v>
+        <v>5.8871</v>
       </c>
       <c r="E7" t="n">
-        <v>3.423100000000001</v>
+        <v>2.15</v>
       </c>
       <c r="F7" t="n">
-        <v>1.119</v>
+        <v>3.7373</v>
       </c>
       <c r="G7" t="n">
-        <v>4.795100000000001</v>
+        <v>3.422800000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9963</v>
+        <v>3.9467</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7986</v>
+        <v>-0.5239000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>9.2759</v>
+        <v>4.714399999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>2.692</v>
+        <v>4.4623</v>
       </c>
       <c r="L7" t="n">
-        <v>6.584</v>
+        <v>0.2522</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.4808</v>
+        <v>-1.2915</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6957</v>
+        <v>-0.5156000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.7851</v>
+        <v>-0.7759999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3894000000000002</v>
+        <v>2.142</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.0369</v>
+        <v>-1.5579</v>
       </c>
       <c r="R7" t="n">
-        <v>5.6475</v>
+        <v>3.7</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4695999999999999</v>
+        <v>0.8124</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.9271</v>
+        <v>-0.8518</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4574</v>
+        <v>1.6642</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6061000000000001</v>
+        <v>-0.4901</v>
       </c>
       <c r="W7" t="n">
-        <v>2.111</v>
+        <v>-0.1547999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5049</v>
+        <v>-0.3354</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4.0179</v>
+        <v>5.7948</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9297000000000001</v>
+        <v>5.7948</v>
       </c>
       <c r="F8" t="n">
-        <v>3.088</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.422800000000001</v>
+        <v>5.7948</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9467</v>
+        <v>1.5395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5239000000000001</v>
+        <v>4.2553</v>
       </c>
       <c r="J8" t="n">
-        <v>4.714399999999999</v>
+        <v>5.7948</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4623</v>
+        <v>1.5395</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2522</v>
+        <v>4.2553</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2915</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5156000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7759999999999999</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.142</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.5579</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0569</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.0718</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.015</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4901</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1547999999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3213</v>
+        <v>2.5107</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1409</v>
+        <v>1.3024</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1806</v>
+        <v>1.2083</v>
       </c>
       <c r="G9" t="n">
         <v>1.6889</v>
@@ -1156,13 +1156,13 @@
         <v>2.5315</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3185000000000002</v>
+        <v>0.5077999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.04899999999999993</v>
+        <v>0.2104</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2696</v>
+        <v>0.2973</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0491</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RUIZ CANAMERO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2147</v>
+        <v>1.682</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8772</v>
+        <v>-3.9943</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3375999999999999</v>
+        <v>5.6764</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2114</v>
+        <v>-2.2158</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8341</v>
+        <v>1.723</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3772</v>
+        <v>-3.9389</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1742</v>
+        <v>-2.1244</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.3541000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2837</v>
+        <v>-2.4786</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0371</v>
+        <v>-0.09150000000000003</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9435</v>
+        <v>1.3688</v>
       </c>
       <c r="O10" t="n">
-        <v>0.09339999999999998</v>
+        <v>-1.4601</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1947</v>
+        <v>2.921</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.7527</v>
+        <v>-2.7264</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9473</v>
+        <v>5.6474</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3091</v>
+        <v>-0.2441</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2344</v>
+        <v>-0.6439999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07449999999999998</v>
+        <v>0.4</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5005</v>
+        <v>1.221</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2211</v>
+        <v>1.5005</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7216</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2532000000000005</v>
+        <v>1.0904</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7564</v>
+        <v>0.5024</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0097</v>
+        <v>0.5879000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.3265</v>
+        <v>2.2114</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6254</v>
+        <v>1.8341</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.701</v>
+        <v>0.3772</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.826</v>
+        <v>1.1742</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.8403</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>1.0145</v>
+        <v>0.2837</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5006</v>
+        <v>1.0371</v>
       </c>
       <c r="N11" t="n">
-        <v>2.215</v>
+        <v>0.9435</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.7154</v>
+        <v>0.09339999999999998</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5579</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.9842</v>
+        <v>-1.7527</v>
       </c>
       <c r="R11" t="n">
-        <v>6.426299999999999</v>
+        <v>1.9473</v>
       </c>
       <c r="S11" t="n">
-        <v>8.027699999999999</v>
+        <v>0.1849</v>
       </c>
       <c r="T11" t="n">
-        <v>4.7799</v>
+        <v>-0.1403</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2476</v>
+        <v>0.325</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8898999999999999</v>
+        <v>-1.5005</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2737</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.1638</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. COSTA I VAZQUEZ</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6024</v>
+        <v>-3.408</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9772</v>
+        <v>-4.8362</v>
       </c>
       <c r="F12" t="n">
-        <v>4.3748</v>
+        <v>1.4283</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2158</v>
+        <v>-5.3265</v>
       </c>
       <c r="H12" t="n">
-        <v>1.723</v>
+        <v>-1.6254</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.9389</v>
+        <v>-3.701</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1244</v>
+        <v>-2.826</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3541000000000001</v>
+        <v>-3.8403</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.4786</v>
+        <v>1.0145</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.09150000000000003</v>
+        <v>-2.5006</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3688</v>
+        <v>2.215</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4601</v>
+        <v>-4.7154</v>
       </c>
       <c r="P12" t="n">
-        <v>2.921</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.7264</v>
+        <v>-7.9842</v>
       </c>
       <c r="R12" t="n">
-        <v>5.6474</v>
+        <v>6.426299999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.5286</v>
+        <v>4.3663</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6271</v>
+        <v>1.7002</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9016000000000001</v>
+        <v>2.6662</v>
       </c>
       <c r="V12" t="n">
-        <v>1.221</v>
+        <v>-0.8898999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5005</v>
+        <v>4.2737</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2795</v>
+        <v>-5.1638</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.111499999999999</v>
+        <v>-4.4846</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.860099999999999</v>
+        <v>-4.4071</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7487</v>
+        <v>-0.07739999999999991</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.450900000000001</v>
+        <v>-6.2154</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5721999999999999</v>
+        <v>2.3779</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.8787</v>
+        <v>-8.5932</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.3775</v>
+        <v>-3.0806</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2591000000000001</v>
+        <v>1.4552</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.636699999999999</v>
+        <v>-4.5358</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07340000000000013</v>
+        <v>-3.1348</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8314</v>
+        <v>0.9227000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7579999999999999</v>
+        <v>-4.0575</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3632</v>
+        <v>-5.4526</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9473</v>
+        <v>6.2314</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6274000000000001</v>
+        <v>1.5108</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1194</v>
+        <v>-0.1476</v>
       </c>
       <c r="U13" t="n">
-        <v>0.492</v>
+        <v>1.6583</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3826</v>
+        <v>-0.5589999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>4.2737</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3826</v>
+        <v>-4.8326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.0909</v>
+        <v>-5.7568</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.947</v>
+        <v>-8.5611</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1439</v>
+        <v>2.8043</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.2154</v>
+        <v>-6.450900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3779</v>
+        <v>-0.5721999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.5932</v>
+        <v>-5.8787</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.0806</v>
+        <v>-6.3775</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4552</v>
+        <v>0.2591000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.5358</v>
+        <v>-6.636699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.1348</v>
+        <v>-0.07340000000000013</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9227000000000001</v>
+        <v>-0.8314</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.0575</v>
+        <v>0.7579999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7789</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.4526</v>
+        <v>-1.3632</v>
       </c>
       <c r="R14" t="n">
-        <v>6.2314</v>
+        <v>1.9473</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0956</v>
+        <v>-0.2727</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.6875</v>
+        <v>-0.8204</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5919</v>
+        <v>0.5477</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5589999999999999</v>
+        <v>0.3826</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2737</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.8326</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>54.8319</v>
+        <v>60.0095</v>
       </c>
       <c r="E15" t="n">
-        <v>28.8133</v>
+        <v>30.6684</v>
       </c>
       <c r="F15" t="n">
-        <v>26.0188</v>
+        <v>29.3416</v>
       </c>
       <c r="G15" t="n">
         <v>22.19159999999999</v>
@@ -1618,19 +1618,19 @@
         <v>2.9208</v>
       </c>
       <c r="Q15" t="n">
-        <v>-50.6319</v>
+        <v>-50.63189999999999</v>
       </c>
       <c r="R15" t="n">
         <v>53.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>13.3087</v>
+        <v>18.486</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5853000000000002</v>
+        <v>1.2698</v>
       </c>
       <c r="U15" t="n">
-        <v>13.8933</v>
+        <v>17.216</v>
       </c>
       <c r="V15" t="n">
         <v>16.4109</v>
